--- a/healthcare_app_frontend/healthcare_app_web/public/template.xlsx
+++ b/healthcare_app_frontend/healthcare_app_web/public/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\healthcare_fe\healthcare_app_frontend\healthcare_app_web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B2C4F1-97C0-420A-A5DC-0D46267409F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E342173-8197-4DF7-9270-96F580AFD820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
     <t>Ngày lập:</t>
   </si>
   <si>
-    <t xml:space="preserve">Người lập: </t>
+    <t>Người lập:</t>
   </si>
 </sst>
 </file>
@@ -57,7 +57,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0\ [$₫-42A];[Red]#,##0\ [$₫-42A]"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ [$₫-42A];[Red]#,##0\ [$₫-42A]"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -159,16 +159,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +534,7 @@
     <col min="3" max="3" width="26.21875" customWidth="1"/>
     <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -545,11 +545,11 @@
       <c r="F1"/>
     </row>
     <row r="2" spans="1:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="10"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
@@ -602,7 +602,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="11"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
@@ -610,7 +610,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
@@ -618,7 +618,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="11"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
@@ -626,7 +626,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="11"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
@@ -634,7 +634,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="11"/>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
@@ -642,7 +642,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
@@ -650,7 +650,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="11"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
@@ -658,7 +658,7 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
@@ -666,7 +666,7 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="11"/>
+      <c r="F16" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
